--- a/0_1_SELECT_ZIVE_DATA_2026/AtsisiustiDuomenys_2026/KJ_-_2026-03-13_2225_to_2026-03-14_0636_8h_10min_test/KJ_10min_test_records_summary_updated.xlsx
+++ b/0_1_SELECT_ZIVE_DATA_2026/AtsisiustiDuomenys_2026/KJ_-_2026-03-13_2225_to_2026-03-14_0636_8h_10min_test/KJ_10min_test_records_summary_updated.xlsx
@@ -672,16 +672,16 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -764,16 +764,16 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -856,16 +856,16 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>718</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -948,16 +948,16 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>

--- a/0_1_SELECT_ZIVE_DATA_2026/AtsisiustiDuomenys_2026/KJ_-_2026-03-13_2225_to_2026-03-14_0636_8h_10min_test/KJ_10min_test_records_summary_updated.xlsx
+++ b/0_1_SELECT_ZIVE_DATA_2026/AtsisiustiDuomenys_2026/KJ_-_2026-03-13_2225_to_2026-03-14_0636_8h_10min_test/KJ_10min_test_records_summary_updated.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Records" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,20 +14,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Records'!$A$1:$AG$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,13 +63,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -429,20 +435,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AG6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="1" max="2"/>
+    <col width="10" customWidth="1" min="3" max="12"/>
     <col hidden="1" width="10" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="10" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="10" customWidth="1" min="15" max="15"/>
@@ -450,19 +446,14 @@
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="20" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="23" max="26"/>
     <col hidden="1" width="11" customWidth="1" min="27" max="27"/>
     <col hidden="1" width="11" customWidth="1" min="28" max="28"/>
     <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="26" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="31" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
@@ -647,6 +638,14 @@
       <c r="C2" t="n">
         <v>128000</v>
       </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N,Ž</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>697</v>
       </c>
@@ -739,6 +738,19 @@
       <c r="C3" t="n">
         <v>128000</v>
       </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ect10</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>729</v>
       </c>
@@ -831,6 +843,9 @@
       <c r="C4" t="n">
         <v>128000</v>
       </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" t="n">
         <v>721</v>
       </c>
@@ -923,6 +938,14 @@
       <c r="C5" t="n">
         <v>128000</v>
       </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>471</v>
       </c>
@@ -1014,6 +1037,19 @@
       </c>
       <c r="C6" t="n">
         <v>128000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ect9</t>
+        </is>
       </c>
       <c r="H6" t="n">
         <v>274</v>
@@ -1106,14 +1142,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Unet model dir:</t>
         </is>
@@ -1125,7 +1161,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Unet model:</t>
         </is>
@@ -1137,7 +1173,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>threshold:</t>
         </is>
@@ -1150,7 +1186,7 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Ectopy model dir:</t>
         </is>
@@ -1162,7 +1198,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Ectopy model:</t>
         </is>
@@ -1174,7 +1210,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Ectopy scaler:</t>
         </is>
@@ -1197,7 +1233,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -1258,7 +1294,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
